--- a/e2e/expectedData/moju_Gaji_Ke-13_yearly.xlsx
+++ b/e2e/expectedData/moju_Gaji_Ke-13_yearly.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>DAFTAR PEMBAYARAN KARYAWAN</t>
   </si>
@@ -50,10 +50,13 @@
     <t>BDD 13th Month Salary Basic Local</t>
   </si>
   <si>
+    <t>1,150.00</t>
+  </si>
+  <si>
     <t>BDD 13th Month Salary Basic Expat</t>
   </si>
   <si>
-    <t>2,730.00</t>
+    <t>1,430.00</t>
   </si>
   <si>
     <t>BDD 13th Month Salary Position Homestaff</t>
@@ -116,16 +119,16 @@
     <t>TL20000002</t>
   </si>
   <si>
-    <t>4,864.00</t>
+    <t>4,654.00</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>5,161.00</t>
-  </si>
-  <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>4,901.00</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -645,7 +648,9 @@
       <c r="C7" s="3">
         <v>11804052</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5">
@@ -653,13 +658,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3">
         <v>11804052</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -668,7 +673,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>11804052</v>
@@ -683,12 +688,14 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>11804052</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>230.0</v>
+      </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5">
@@ -696,13 +703,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3">
         <v>11804052</v>
       </c>
       <c r="D11" s="4">
-        <v>510.0</v>
+        <v>230.0</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -711,7 +718,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3">
         <v>11804052</v>
@@ -726,7 +733,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <v>11804052</v>
@@ -741,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3">
         <v>11804052</v>
@@ -756,7 +763,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <v>11804052</v>
@@ -771,12 +778,14 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3">
         <v>11804052</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>10.0</v>
+      </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5">
@@ -784,13 +793,13 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3">
         <v>11804052</v>
       </c>
       <c r="D17" s="4">
-        <v>120.0</v>
+        <v>100.0</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -799,12 +808,14 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3">
         <v>51114007</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>55.0</v>
+      </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5">
@@ -812,13 +823,13 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3">
         <v>51114007</v>
       </c>
       <c r="D19" s="4">
-        <v>227.0</v>
+        <v>122.0</v>
       </c>
       <c r="E19" s="4"/>
     </row>
@@ -827,7 +838,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" s="3">
         <v>51114007</v>
@@ -842,7 +853,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3">
         <v>51171004</v>
@@ -855,7 +866,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3">
         <v>20501024</v>
@@ -868,7 +879,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" s="3">
         <v>20501024</v>
@@ -881,10 +892,10 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -894,14 +905,14 @@
         <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" s="3">
         <v>20501024</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4">
-        <v>297.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -909,32 +920,32 @@
         <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
@@ -943,23 +954,23 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30"/>
       <c r="D30" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E30" s="8"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31"/>
       <c r="D31" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" s="7"/>
     </row>
@@ -972,23 +983,23 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33"/>
       <c r="D33" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E33" s="7"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34"/>
       <c r="D34" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E34" s="7"/>
     </row>

--- a/e2e/expectedData/moju_Gaji_Ke-13_yearly.xlsx
+++ b/e2e/expectedData/moju_Gaji_Ke-13_yearly.xlsx
@@ -56,7 +56,7 @@
     <t>BDD 13th Month Salary Basic Expat</t>
   </si>
   <si>
-    <t>1,430.00</t>
+    <t>1,310.00</t>
   </si>
   <si>
     <t>BDD 13th Month Salary Position Homestaff</t>
@@ -119,16 +119,16 @@
     <t>TL20000002</t>
   </si>
   <si>
-    <t>4,654.00</t>
+    <t>4,474.00</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>4,901.00</t>
-  </si>
-  <si>
-    <t>DILI, 09 September 2026</t>
+    <t>4,721.00</t>
+  </si>
+  <si>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -709,7 +709,7 @@
         <v>11804052</v>
       </c>
       <c r="D11" s="4">
-        <v>230.0</v>
+        <v>220.0</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -799,7 +799,7 @@
         <v>11804052</v>
       </c>
       <c r="D17" s="4">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="E17" s="4"/>
     </row>
